--- a/grid_search_results.xlsx
+++ b/grid_search_results.xlsx
@@ -454,10 +454,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8113792176367791</v>
+        <v>0.812535287000941</v>
       </c>
       <c r="C2" t="n">
-        <v>0.9074074074074074</v>
+        <v>0.8755760368663594</v>
       </c>
     </row>
     <row r="3">
@@ -467,10 +467,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8229533539454227</v>
+        <v>0.8333646995563919</v>
       </c>
       <c r="C3" t="n">
-        <v>0.8981481481481481</v>
+        <v>0.8663594470046083</v>
       </c>
     </row>
   </sheetData>
@@ -581,16 +581,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>0.3962831497192383</v>
+        <v>0.403821325302124</v>
       </c>
       <c r="B2" t="n">
-        <v>0.006853219818488875</v>
+        <v>0.01597131628504408</v>
       </c>
       <c r="C2" t="n">
-        <v>0.01799502372741699</v>
+        <v>0.0165252685546875</v>
       </c>
       <c r="D2" t="n">
-        <v>0.001566988517405634</v>
+        <v>0.001554332495619839</v>
       </c>
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="n">
@@ -611,42 +611,42 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L2" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M2" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="O2" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="P2" t="n">
-        <v>0.8090805215754806</v>
+        <v>0.8322153515257427</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.02988962729982617</v>
+        <v>0.02042183588010777</v>
       </c>
       <c r="R2" t="n">
-        <v>35</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.5621501445770264</v>
+        <v>0.6373492240905761</v>
       </c>
       <c r="B3" t="n">
-        <v>0.02372114192768984</v>
+        <v>0.0543346207234824</v>
       </c>
       <c r="C3" t="n">
-        <v>0.01763710975646973</v>
+        <v>0.02020559310913086</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001564334902821889</v>
+        <v>0.00532880772750092</v>
       </c>
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="n">
@@ -667,42 +667,42 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.8554913294797688</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M3" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N3" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="P3" t="n">
-        <v>0.8148675897298023</v>
+        <v>0.819471703185912</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.03653828670658316</v>
+        <v>0.03160756948968823</v>
       </c>
       <c r="R3" t="n">
-        <v>16</v>
+        <v>31</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.7875764846801758</v>
+        <v>0.8140103816986084</v>
       </c>
       <c r="B4" t="n">
-        <v>0.01962813741251962</v>
+        <v>0.03431185600800411</v>
       </c>
       <c r="C4" t="n">
-        <v>0.02949490547180176</v>
+        <v>0.03024659156799316</v>
       </c>
       <c r="D4" t="n">
-        <v>0.002893326843404641</v>
+        <v>0.002968514414813083</v>
       </c>
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="n">
@@ -723,42 +723,42 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.8497109826589595</v>
       </c>
       <c r="N4" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="O4" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="P4" t="n">
-        <v>0.8217905632477484</v>
+        <v>0.8287404220997445</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.02025054689159044</v>
+        <v>0.02851214710591666</v>
       </c>
       <c r="R4" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1.116495323181152</v>
+        <v>1.219006872177124</v>
       </c>
       <c r="B5" t="n">
-        <v>0.01672340713955309</v>
+        <v>0.07365124399753889</v>
       </c>
       <c r="C5" t="n">
-        <v>0.02865214347839356</v>
+        <v>0.02941203117370605</v>
       </c>
       <c r="D5" t="n">
-        <v>0.002666007759849855</v>
+        <v>0.001919355793313012</v>
       </c>
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="n">
@@ -779,42 +779,42 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L5" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M5" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7398843930635838</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8546511627906976</v>
       </c>
       <c r="P5" t="n">
-        <v>0.8125554510014787</v>
+        <v>0.8125487296679662</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.03132834820178915</v>
+        <v>0.03878140941448852</v>
       </c>
       <c r="R5" t="n">
-        <v>24</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.3955263614654541</v>
+        <v>0.4465607166290283</v>
       </c>
       <c r="B6" t="n">
-        <v>0.01630112008936465</v>
+        <v>0.03295182512327556</v>
       </c>
       <c r="C6" t="n">
-        <v>0.01559829711914062</v>
+        <v>0.0202235221862793</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0002543349008398945</v>
+        <v>0.003470906421913961</v>
       </c>
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="n">
@@ -835,42 +835,42 @@
         </is>
       </c>
       <c r="K6" t="n">
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.838150289017341</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.791907514450867</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="O6" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.8546511627906976</v>
       </c>
       <c r="P6" t="n">
-        <v>0.817166285791101</v>
+        <v>0.8264215620379083</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.02246544369062494</v>
+        <v>0.01801455313902122</v>
       </c>
       <c r="R6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.5471705913543701</v>
+        <v>0.6098053455352783</v>
       </c>
       <c r="B7" t="n">
-        <v>0.01021750089924178</v>
+        <v>0.03598648230581696</v>
       </c>
       <c r="C7" t="n">
-        <v>0.01664109230041504</v>
+        <v>0.0186561107635498</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001471545200036426</v>
+        <v>0.001905598317750234</v>
       </c>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="n">
@@ -891,42 +891,42 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="L7" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="N7" t="n">
-        <v>0.8265895953757225</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="P7" t="n">
-        <v>0.8148407043957521</v>
+        <v>0.8113792176367791</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.02204410498342036</v>
+        <v>0.02679757487541312</v>
       </c>
       <c r="R7" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>0.789403772354126</v>
+        <v>0.8476047039031982</v>
       </c>
       <c r="B8" t="n">
-        <v>0.0471715957258573</v>
+        <v>0.01460115350699976</v>
       </c>
       <c r="C8" t="n">
-        <v>0.02808723449707031</v>
+        <v>0.02903566360473633</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002245867077930718</v>
+        <v>0.001216318514981622</v>
       </c>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="n">
@@ -947,42 +947,42 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L8" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M8" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N8" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O8" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8546511627906976</v>
       </c>
       <c r="P8" t="n">
-        <v>0.8171595644575884</v>
+        <v>0.8229533539454227</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02421896715847448</v>
+        <v>0.02631029408932139</v>
       </c>
       <c r="R8" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1.086483144760132</v>
+        <v>1.176901245117187</v>
       </c>
       <c r="B9" t="n">
-        <v>0.01324417295686051</v>
+        <v>0.05192808113740779</v>
       </c>
       <c r="C9" t="n">
-        <v>0.03018765449523926</v>
+        <v>0.03024249076843262</v>
       </c>
       <c r="D9" t="n">
-        <v>0.004771085313589446</v>
+        <v>0.002563162649432209</v>
       </c>
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="n">
@@ -1003,42 +1003,42 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L9" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N9" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P9" t="n">
-        <v>0.8136980776986155</v>
+        <v>0.8148339830622395</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.028428949374359</v>
+        <v>0.02913330513082046</v>
       </c>
       <c r="R9" t="n">
-        <v>21</v>
+        <v>38</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.3941435813903809</v>
+        <v>0.4130263328552246</v>
       </c>
       <c r="B10" t="n">
-        <v>0.02349557030674945</v>
+        <v>0.01340256987332294</v>
       </c>
       <c r="C10" t="n">
-        <v>0.01675329208374023</v>
+        <v>0.01785063743591309</v>
       </c>
       <c r="D10" t="n">
-        <v>0.001584591410897418</v>
+        <v>0.003212739347816803</v>
       </c>
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="n">
@@ -1059,42 +1059,42 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L10" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="M10" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N10" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O10" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P10" t="n">
-        <v>0.8183357978222879</v>
+        <v>0.8217905632477482</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03157048057066171</v>
+        <v>0.03073569910234576</v>
       </c>
       <c r="R10" t="n">
-        <v>8</v>
+        <v>27</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.5374547958374023</v>
+        <v>0.5641293525695801</v>
       </c>
       <c r="B11" t="n">
-        <v>0.007298492275276409</v>
+        <v>0.0294471313429609</v>
       </c>
       <c r="C11" t="n">
-        <v>0.01720800399780274</v>
+        <v>0.01651554107666016</v>
       </c>
       <c r="D11" t="n">
-        <v>0.001380106028201215</v>
+        <v>0.0007495033389841937</v>
       </c>
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="n">
@@ -1115,42 +1115,42 @@
         </is>
       </c>
       <c r="K11" t="n">
+        <v>0.8034682080924855</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.815028901734104</v>
+      </c>
+      <c r="M11" t="n">
         <v>0.8439306358381503</v>
       </c>
-      <c r="L11" t="n">
-        <v>0.7803468208092486</v>
-      </c>
-      <c r="M11" t="n">
-        <v>0.7803468208092486</v>
-      </c>
       <c r="N11" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O11" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="P11" t="n">
-        <v>0.8125554510014787</v>
+        <v>0.8136846350315903</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03339333823576052</v>
+        <v>0.0267966004443215</v>
       </c>
       <c r="R11" t="n">
-        <v>24</v>
+        <v>41</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>0.7815979957580567</v>
+        <v>0.7765907287597656</v>
       </c>
       <c r="B12" t="n">
-        <v>0.03446689339884565</v>
+        <v>0.01586807020023378</v>
       </c>
       <c r="C12" t="n">
-        <v>0.02974610328674316</v>
+        <v>0.02698454856872558</v>
       </c>
       <c r="D12" t="n">
-        <v>0.00240388726930416</v>
+        <v>0.0004194869740407409</v>
       </c>
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="n">
@@ -1174,39 +1174,39 @@
         <v>0.8439306358381503</v>
       </c>
       <c r="L12" t="n">
-        <v>0.791907514450867</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M12" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.8554913294797688</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O12" t="n">
         <v>0.8430232558139535</v>
       </c>
       <c r="P12" t="n">
-        <v>0.819471703185912</v>
+        <v>0.8298763274633687</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.02185874797172915</v>
+        <v>0.0310707729199617</v>
       </c>
       <c r="R12" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1.08913459777832</v>
+        <v>1.12957501411438</v>
       </c>
       <c r="B13" t="n">
-        <v>0.0167720275862877</v>
+        <v>0.04950130918944098</v>
       </c>
       <c r="C13" t="n">
-        <v>0.03108348846435547</v>
+        <v>0.02919611930847168</v>
       </c>
       <c r="D13" t="n">
-        <v>0.004371032639458834</v>
+        <v>0.001422378800031587</v>
       </c>
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="n">
@@ -1227,42 +1227,42 @@
         </is>
       </c>
       <c r="K13" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="L13" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M13" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O13" t="n">
-        <v>0.8662790697674418</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P13" t="n">
-        <v>0.814874311063315</v>
+        <v>0.8194784245194245</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.03521814314961457</v>
+        <v>0.03460938306913399</v>
       </c>
       <c r="R13" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>0.383535099029541</v>
+        <v>0.3912291526794434</v>
       </c>
       <c r="B14" t="n">
-        <v>0.01142637310588813</v>
+        <v>0.007446821575233908</v>
       </c>
       <c r="C14" t="n">
-        <v>0.01560015678405762</v>
+        <v>0.01852278709411621</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0001457140862024649</v>
+        <v>0.003147506298491197</v>
       </c>
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="n">
@@ -1283,42 +1283,42 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.8554913294797688</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="N14" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P14" t="n">
-        <v>0.8194851458529373</v>
+        <v>0.8113859389702917</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.02958889192954923</v>
+        <v>0.0324135679715757</v>
       </c>
       <c r="R14" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>0.5365810394287109</v>
+        <v>0.547091293334961</v>
       </c>
       <c r="B15" t="n">
-        <v>0.003522369482911552</v>
+        <v>0.01405458957154749</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01710982322692871</v>
+        <v>0.0167032241821289</v>
       </c>
       <c r="D15" t="n">
-        <v>0.001363187755611815</v>
+        <v>0.0009845312313478182</v>
       </c>
       <c r="E15" t="inlineStr"/>
       <c r="F15" t="n">
@@ -1339,42 +1339,42 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M15" t="n">
-        <v>0.791907514450867</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="N15" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8313953488372093</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="P15" t="n">
-        <v>0.8125218443339157</v>
+        <v>0.8159766097593761</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.0305950465036261</v>
+        <v>0.02432387729981052</v>
       </c>
       <c r="R15" t="n">
-        <v>29</v>
+        <v>37</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>0.7870234966278076</v>
+        <v>0.7861018657684327</v>
       </c>
       <c r="B16" t="n">
-        <v>0.03544890387940719</v>
+        <v>0.01572140268322575</v>
       </c>
       <c r="C16" t="n">
-        <v>0.02866353988647461</v>
+        <v>0.02806601524353027</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0003293922130368735</v>
+        <v>0.001006309445169552</v>
       </c>
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="n">
@@ -1395,42 +1395,42 @@
         </is>
       </c>
       <c r="K16" t="n">
+        <v>0.8092485549132948</v>
+      </c>
+      <c r="L16" t="n">
+        <v>0.8265895953757225</v>
+      </c>
+      <c r="M16" t="n">
         <v>0.8439306358381503</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.7687861271676301</v>
-      </c>
-      <c r="M16" t="n">
-        <v>0.8092485549132948</v>
-      </c>
       <c r="N16" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8779069767441861</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8102164269391047</v>
+        <v>0.8264484473719586</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.02799244896479366</v>
+        <v>0.03447086463736185</v>
       </c>
       <c r="R16" t="n">
-        <v>32</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1.077506923675537</v>
+        <v>1.068727159500122</v>
       </c>
       <c r="B17" t="n">
-        <v>0.02090130132752154</v>
+        <v>0.02473483547079441</v>
       </c>
       <c r="C17" t="n">
-        <v>0.02942075729370117</v>
+        <v>0.0273554801940918</v>
       </c>
       <c r="D17" t="n">
-        <v>0.002177809939156318</v>
+        <v>0.0005008891073584707</v>
       </c>
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="n">
@@ -1454,39 +1454,39 @@
         <v>0.838150289017341</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7630057803468208</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8662790697674418</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P17" t="n">
-        <v>0.8067818255141821</v>
+        <v>0.8159900524264014</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.03889902074046594</v>
+        <v>0.03524386586390792</v>
       </c>
       <c r="R17" t="n">
-        <v>39</v>
+        <v>36</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>0.3978647232055664</v>
+        <v>0.4168073177337647</v>
       </c>
       <c r="B18" t="n">
-        <v>0.01198226889251048</v>
+        <v>0.02152298725709825</v>
       </c>
       <c r="C18" t="n">
-        <v>0.01777167320251465</v>
+        <v>0.01813535690307617</v>
       </c>
       <c r="D18" t="n">
-        <v>0.00234247736598557</v>
+        <v>0.001139135292493814</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
@@ -1509,42 +1509,42 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M18" t="n">
+        <v>0.8554913294797688</v>
+      </c>
+      <c r="N18" t="n">
         <v>0.7803468208092486</v>
       </c>
-      <c r="N18" t="n">
-        <v>0.7745664739884393</v>
-      </c>
       <c r="O18" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8546511627906976</v>
       </c>
       <c r="P18" t="n">
-        <v>0.8067549401801317</v>
+        <v>0.829889770130394</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.02869409936533044</v>
+        <v>0.02735000051891739</v>
       </c>
       <c r="R18" t="n">
-        <v>40</v>
+        <v>5</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>0.5548191547393799</v>
+        <v>0.562009048461914</v>
       </c>
       <c r="B19" t="n">
-        <v>0.01974493121279263</v>
+        <v>0.01754259452172434</v>
       </c>
       <c r="C19" t="n">
-        <v>0.01692094802856445</v>
+        <v>0.01679506301879883</v>
       </c>
       <c r="D19" t="n">
-        <v>0.00151884662086067</v>
+        <v>0.001000438979143452</v>
       </c>
       <c r="E19" t="n">
         <v>10</v>
@@ -1567,42 +1567,42 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="L19" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7572254335260116</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="N19" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O19" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="P19" t="n">
-        <v>0.8033001747546713</v>
+        <v>0.8194649818523996</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.03793956710126557</v>
+        <v>0.02922127862741166</v>
       </c>
       <c r="R19" t="n">
-        <v>43</v>
+        <v>32</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>0.7864924907684326</v>
+        <v>0.8146214485168457</v>
       </c>
       <c r="B20" t="n">
-        <v>0.0195499163024647</v>
+        <v>0.04353521065774098</v>
       </c>
       <c r="C20" t="n">
-        <v>0.03006868362426758</v>
+        <v>0.02944002151489258</v>
       </c>
       <c r="D20" t="n">
-        <v>0.003154836453094204</v>
+        <v>0.001658000790640993</v>
       </c>
       <c r="E20" t="n">
         <v>10</v>
@@ -1625,42 +1625,42 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="N20" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O20" t="n">
         <v>0.8604651162790697</v>
       </c>
       <c r="P20" t="n">
-        <v>0.8183357978222879</v>
+        <v>0.825272214007259</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02868711757469827</v>
+        <v>0.02820967296681976</v>
       </c>
       <c r="R20" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1.127472114562988</v>
+        <v>1.155809783935547</v>
       </c>
       <c r="B21" t="n">
-        <v>0.05764975508852867</v>
+        <v>0.04217259477937518</v>
       </c>
       <c r="C21" t="n">
-        <v>0.02864489555358887</v>
+        <v>0.03235306739807129</v>
       </c>
       <c r="D21" t="n">
-        <v>0.002434752123707432</v>
+        <v>0.005068528956887988</v>
       </c>
       <c r="E21" t="n">
         <v>10</v>
@@ -1683,42 +1683,42 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L21" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="M21" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="N21" t="n">
         <v>0.7745664739884393</v>
       </c>
-      <c r="M21" t="n">
-        <v>0.7861271676300579</v>
-      </c>
-      <c r="N21" t="n">
-        <v>0.8092485549132948</v>
-      </c>
       <c r="O21" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8102164269391047</v>
+        <v>0.8183156338217502</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.02726687198422237</v>
+        <v>0.02450189649128927</v>
       </c>
       <c r="R21" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>0.383955717086792</v>
+        <v>0.4255909442901611</v>
       </c>
       <c r="B22" t="n">
-        <v>0.01190785800165682</v>
+        <v>0.02780037954786226</v>
       </c>
       <c r="C22" t="n">
-        <v>0.01573548316955566</v>
+        <v>0.01702775955200195</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003830482961497663</v>
+        <v>0.001106361923163191</v>
       </c>
       <c r="E22" t="n">
         <v>10</v>
@@ -1741,42 +1741,42 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N22" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O22" t="n">
         <v>0.8488372093023255</v>
       </c>
       <c r="P22" t="n">
-        <v>0.8148541470627773</v>
+        <v>0.817166285791101</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.02834189891440553</v>
+        <v>0.03203013809477782</v>
       </c>
       <c r="R22" t="n">
-        <v>18</v>
+        <v>35</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>0.5526795864105225</v>
+        <v>0.6150037288665772</v>
       </c>
       <c r="B23" t="n">
-        <v>0.009538281248039378</v>
+        <v>0.05743262088405367</v>
       </c>
       <c r="C23" t="n">
-        <v>0.01700649261474609</v>
+        <v>0.02014212608337402</v>
       </c>
       <c r="D23" t="n">
-        <v>0.00146819990449604</v>
+        <v>0.004783629364374045</v>
       </c>
       <c r="E23" t="n">
         <v>10</v>
@@ -1799,42 +1799,42 @@
         </is>
       </c>
       <c r="K23" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L23" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M23" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O23" t="n">
         <v>0.8430232558139535</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8032867320876462</v>
+        <v>0.8136913563651028</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.03226883869540229</v>
+        <v>0.02750220196810746</v>
       </c>
       <c r="R23" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>0.7683351993560791</v>
+        <v>0.9576592922210694</v>
       </c>
       <c r="B24" t="n">
-        <v>0.00463666318167165</v>
+        <v>0.05256063545047331</v>
       </c>
       <c r="C24" t="n">
-        <v>0.02844324111938477</v>
+        <v>0.02886490821838379</v>
       </c>
       <c r="D24" t="n">
-        <v>0.001991617653016833</v>
+        <v>0.001617499161156647</v>
       </c>
       <c r="E24" t="n">
         <v>10</v>
@@ -1857,42 +1857,42 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="M24" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N24" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="P24" t="n">
-        <v>0.8125487296679662</v>
+        <v>0.8218107272482861</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.02867724821264845</v>
+        <v>0.03337901384691008</v>
       </c>
       <c r="R24" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1.088914155960083</v>
+        <v>1.212029027938843</v>
       </c>
       <c r="B25" t="n">
-        <v>0.02325208981019699</v>
+        <v>0.06355209626301866</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0291468620300293</v>
+        <v>0.03107185363769531</v>
       </c>
       <c r="D25" t="n">
-        <v>0.002968428679907223</v>
+        <v>0.00372733705034586</v>
       </c>
       <c r="E25" t="n">
         <v>10</v>
@@ -1915,42 +1915,42 @@
         </is>
       </c>
       <c r="K25" t="n">
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="L25" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="M25" t="n">
         <v>0.838150289017341</v>
       </c>
-      <c r="L25" t="n">
-        <v>0.7572254335260116</v>
-      </c>
-      <c r="M25" t="n">
-        <v>0.7745664739884393</v>
-      </c>
       <c r="N25" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8255813953488372</v>
       </c>
       <c r="P25" t="n">
-        <v>0.8032867320876461</v>
+        <v>0.8136711923645651</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.03388506545264712</v>
+        <v>0.03166626730465004</v>
       </c>
       <c r="R25" t="n">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>0.3926073551177979</v>
+        <v>0.4236214637756348</v>
       </c>
       <c r="B26" t="n">
-        <v>0.02607471438199602</v>
+        <v>0.0274768705430342</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0169881820678711</v>
+        <v>0.01689448356628418</v>
       </c>
       <c r="D26" t="n">
-        <v>0.002458284310679241</v>
+        <v>0.001388639778586246</v>
       </c>
       <c r="E26" t="n">
         <v>10</v>
@@ -1973,42 +1973,42 @@
         </is>
       </c>
       <c r="K26" t="n">
+        <v>0.815028901734104</v>
+      </c>
+      <c r="L26" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="M26" t="n">
         <v>0.838150289017341</v>
       </c>
-      <c r="L26" t="n">
-        <v>0.7630057803468208</v>
-      </c>
-      <c r="M26" t="n">
-        <v>0.8092485549132948</v>
-      </c>
       <c r="N26" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8779069767441861</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8067549401801317</v>
+        <v>0.8264484473719586</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.03136448474561453</v>
+        <v>0.03542690118518697</v>
       </c>
       <c r="R26" t="n">
-        <v>40</v>
+        <v>8</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>0.5492510318756103</v>
+        <v>0.554438591003418</v>
       </c>
       <c r="B27" t="n">
-        <v>0.0177916883746532</v>
+        <v>0.02598556511571138</v>
       </c>
       <c r="C27" t="n">
-        <v>0.01799716949462891</v>
+        <v>0.01634716987609863</v>
       </c>
       <c r="D27" t="n">
-        <v>0.002398049513963915</v>
+        <v>0.0004689354901294731</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
@@ -2034,39 +2034,39 @@
         <v>0.8439306358381503</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7398843930635838</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="M27" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="N27" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O27" t="n">
         <v>0.8313953488372093</v>
       </c>
       <c r="P27" t="n">
-        <v>0.7974929425998118</v>
+        <v>0.8148339830622395</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.03710239658830079</v>
+        <v>0.02772290903495295</v>
       </c>
       <c r="R27" t="n">
-        <v>48</v>
+        <v>38</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>0.8109913825988769</v>
+        <v>0.8550906181335449</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04179946409339861</v>
+        <v>0.06215307746082657</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0309506893157959</v>
+        <v>0.03042597770690918</v>
       </c>
       <c r="D28" t="n">
-        <v>0.005152849172437547</v>
+        <v>0.001919867353755343</v>
       </c>
       <c r="E28" t="n">
         <v>10</v>
@@ -2089,16 +2089,16 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.8554913294797688</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="L28" t="n">
-        <v>0.791907514450867</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M28" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N28" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O28" t="n">
         <v>0.8546511627906976</v>
@@ -2107,24 +2107,24 @@
         <v>0.8206412152170991</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.02881753225494738</v>
+        <v>0.03147744796255508</v>
       </c>
       <c r="R28" t="n">
-        <v>4</v>
+        <v>28</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1.089720964431763</v>
+        <v>1.142852258682251</v>
       </c>
       <c r="B29" t="n">
-        <v>0.02739913029858324</v>
+        <v>0.07908089161525499</v>
       </c>
       <c r="C29" t="n">
-        <v>0.02956304550170898</v>
+        <v>0.03470058441162109</v>
       </c>
       <c r="D29" t="n">
-        <v>0.002212999589841746</v>
+        <v>0.01007264967675522</v>
       </c>
       <c r="E29" t="n">
         <v>10</v>
@@ -2147,42 +2147,42 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8554913294797688</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M29" t="n">
-        <v>0.7630057803468208</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N29" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8009947573598601</v>
+        <v>0.8264148407043959</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.04218570218189812</v>
+        <v>0.03067496441701348</v>
       </c>
       <c r="R29" t="n">
-        <v>46</v>
+        <v>13</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>0.3972359180450439</v>
+        <v>0.3909148693084717</v>
       </c>
       <c r="B30" t="n">
-        <v>0.03497021764530946</v>
+        <v>0.01284206459469391</v>
       </c>
       <c r="C30" t="n">
-        <v>0.01799435615539551</v>
+        <v>0.01770539283752441</v>
       </c>
       <c r="D30" t="n">
-        <v>0.00481900749605337</v>
+        <v>0.001129519248896507</v>
       </c>
       <c r="E30" t="n">
         <v>10</v>
@@ -2205,42 +2205,42 @@
         </is>
       </c>
       <c r="K30" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="L30" t="n">
+        <v>0.838150289017341</v>
+      </c>
+      <c r="M30" t="n">
         <v>0.8439306358381503</v>
       </c>
-      <c r="L30" t="n">
+      <c r="N30" t="n">
         <v>0.7630057803468208</v>
       </c>
-      <c r="M30" t="n">
-        <v>0.7976878612716763</v>
-      </c>
-      <c r="N30" t="n">
-        <v>0.7861271676300579</v>
-      </c>
       <c r="O30" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.8546511627906976</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8079177308778063</v>
+        <v>0.8264215620379083</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.03337033178596732</v>
+        <v>0.03255145359140036</v>
       </c>
       <c r="R30" t="n">
-        <v>38</v>
+        <v>10</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>0.5604246616363525</v>
+        <v>0.6014175891876221</v>
       </c>
       <c r="B31" t="n">
-        <v>0.02555439912968376</v>
+        <v>0.02579698044625416</v>
       </c>
       <c r="C31" t="n">
-        <v>0.0167022705078125</v>
+        <v>0.01718034744262695</v>
       </c>
       <c r="D31" t="n">
-        <v>0.001394083627449849</v>
+        <v>0.0005002364655081488</v>
       </c>
       <c r="E31" t="n">
         <v>10</v>
@@ -2263,42 +2263,42 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.8554913294797688</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7398843930635838</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M31" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="N31" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P31" t="n">
-        <v>0.7998185239951606</v>
+        <v>0.8240825379755343</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.04316596951883451</v>
+        <v>0.02793177573462751</v>
       </c>
       <c r="R31" t="n">
-        <v>47</v>
+        <v>19</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>0.771849536895752</v>
+        <v>0.8192033767700195</v>
       </c>
       <c r="B32" t="n">
-        <v>0.02071141548865827</v>
+        <v>0.01802616292026257</v>
       </c>
       <c r="C32" t="n">
-        <v>0.03141360282897949</v>
+        <v>0.03052277565002441</v>
       </c>
       <c r="D32" t="n">
-        <v>0.005635763635553741</v>
+        <v>0.00343163110915785</v>
       </c>
       <c r="E32" t="n">
         <v>10</v>
@@ -2321,42 +2321,42 @@
         </is>
       </c>
       <c r="K32" t="n">
+        <v>0.8092485549132948</v>
+      </c>
+      <c r="L32" t="n">
+        <v>0.838150289017341</v>
+      </c>
+      <c r="M32" t="n">
         <v>0.8323699421965318</v>
       </c>
-      <c r="L32" t="n">
-        <v>0.7861271676300579</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.8034682080924855</v>
-      </c>
       <c r="N32" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O32" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="P32" t="n">
-        <v>0.8125487296679662</v>
+        <v>0.8241228659766098</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.02699684831266601</v>
+        <v>0.03072135901254523</v>
       </c>
       <c r="R32" t="n">
-        <v>26</v>
+        <v>16</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1.098032379150391</v>
+        <v>1.148631811141968</v>
       </c>
       <c r="B33" t="n">
-        <v>0.02350654802335379</v>
+        <v>0.02519434417818229</v>
       </c>
       <c r="C33" t="n">
-        <v>0.03191890716552735</v>
+        <v>0.0308863639831543</v>
       </c>
       <c r="D33" t="n">
-        <v>0.003939886924416359</v>
+        <v>0.001737721944397269</v>
       </c>
       <c r="E33" t="n">
         <v>10</v>
@@ -2379,42 +2379,42 @@
         </is>
       </c>
       <c r="K33" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8497109826589595</v>
       </c>
       <c r="L33" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M33" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N33" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="P33" t="n">
-        <v>0.809087242908993</v>
+        <v>0.822933189944885</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.03829923177121681</v>
+        <v>0.03062762339652328</v>
       </c>
       <c r="R33" t="n">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>0.4053223133087158</v>
+        <v>0.4183559417724609</v>
       </c>
       <c r="B34" t="n">
-        <v>0.008082657481856593</v>
+        <v>0.006671161292143987</v>
       </c>
       <c r="C34" t="n">
-        <v>0.01655387878417969</v>
+        <v>0.01639294624328613</v>
       </c>
       <c r="D34" t="n">
-        <v>0.0009752310467050907</v>
+        <v>0.0005777008218212753</v>
       </c>
       <c r="E34" t="n">
         <v>20</v>
@@ -2437,25 +2437,25 @@
         </is>
       </c>
       <c r="K34" t="n">
+        <v>0.8265895953757225</v>
+      </c>
+      <c r="L34" t="n">
         <v>0.8497109826589595</v>
       </c>
-      <c r="L34" t="n">
-        <v>0.8034682080924855</v>
-      </c>
       <c r="M34" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.861271676300578</v>
       </c>
       <c r="N34" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O34" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8604651162790697</v>
       </c>
       <c r="P34" t="n">
-        <v>0.8229533539454227</v>
+        <v>0.8333646995563919</v>
       </c>
       <c r="Q34" t="n">
-        <v>0.02419321940309498</v>
+        <v>0.03463156640188862</v>
       </c>
       <c r="R34" t="n">
         <v>1</v>
@@ -2463,16 +2463,16 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>0.5742849349975586</v>
+        <v>0.6302093029022217</v>
       </c>
       <c r="B35" t="n">
-        <v>0.01290600996822994</v>
+        <v>0.04791930358828903</v>
       </c>
       <c r="C35" t="n">
-        <v>0.01694207191467285</v>
+        <v>0.01824936866760254</v>
       </c>
       <c r="D35" t="n">
-        <v>0.0008881966451830686</v>
+        <v>0.002250117311528311</v>
       </c>
       <c r="E35" t="n">
         <v>20</v>
@@ -2495,42 +2495,42 @@
         </is>
       </c>
       <c r="K35" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="L35" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M35" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="N35" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="O35" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="P35" t="n">
-        <v>0.8136980776986155</v>
+        <v>0.8067213335125689</v>
       </c>
       <c r="Q35" t="n">
-        <v>0.03133607651330702</v>
+        <v>0.03215315104614294</v>
       </c>
       <c r="R35" t="n">
-        <v>21</v>
+        <v>48</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>0.8109130382537841</v>
+        <v>0.8607947349548339</v>
       </c>
       <c r="B36" t="n">
-        <v>0.01390393801983894</v>
+        <v>0.05407457244646753</v>
       </c>
       <c r="C36" t="n">
-        <v>0.02955188751220703</v>
+        <v>0.03040580749511719</v>
       </c>
       <c r="D36" t="n">
-        <v>0.001993263271379941</v>
+        <v>0.003827259961796635</v>
       </c>
       <c r="E36" t="n">
         <v>20</v>
@@ -2553,42 +2553,42 @@
         </is>
       </c>
       <c r="K36" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L36" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="M36" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="N36" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.791907514450867</v>
       </c>
       <c r="O36" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="P36" t="n">
-        <v>0.8171595644575884</v>
+        <v>0.8310592821615808</v>
       </c>
       <c r="Q36" t="n">
-        <v>0.02220368491918659</v>
+        <v>0.02675946811096758</v>
       </c>
       <c r="R36" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1.142470932006836</v>
+        <v>1.19532151222229</v>
       </c>
       <c r="B37" t="n">
-        <v>0.0369533132549023</v>
+        <v>0.04740974684661221</v>
       </c>
       <c r="C37" t="n">
-        <v>0.0310551643371582</v>
+        <v>0.03254895210266114</v>
       </c>
       <c r="D37" t="n">
-        <v>0.002715241446966827</v>
+        <v>0.002163334631404518</v>
       </c>
       <c r="E37" t="n">
         <v>20</v>
@@ -2611,42 +2611,42 @@
         </is>
       </c>
       <c r="K37" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L37" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M37" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="N37" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O37" t="n">
-        <v>0.8720930232558139</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P37" t="n">
-        <v>0.8148810323968275</v>
+        <v>0.8113657749697539</v>
       </c>
       <c r="Q37" t="n">
-        <v>0.03759047567240314</v>
+        <v>0.03058768038849878</v>
       </c>
       <c r="R37" t="n">
-        <v>14</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>0.3960041522979736</v>
+        <v>0.4248639583587647</v>
       </c>
       <c r="B38" t="n">
-        <v>0.006289138338803063</v>
+        <v>0.02017181742062606</v>
       </c>
       <c r="C38" t="n">
-        <v>0.01609292030334473</v>
+        <v>0.01729297637939453</v>
       </c>
       <c r="D38" t="n">
-        <v>0.0004584541328974157</v>
+        <v>0.001380941469205804</v>
       </c>
       <c r="E38" t="n">
         <v>20</v>
@@ -2669,42 +2669,42 @@
         </is>
       </c>
       <c r="K38" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L38" t="n">
-        <v>0.815028901734104</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M38" t="n">
-        <v>0.815028901734104</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N38" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O38" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P38" t="n">
-        <v>0.8229399112783977</v>
+        <v>0.8229466326119101</v>
       </c>
       <c r="Q38" t="n">
-        <v>0.02101527438544699</v>
+        <v>0.02582820184226386</v>
       </c>
       <c r="R38" t="n">
-        <v>2</v>
+        <v>22</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>0.5589876651763916</v>
+        <v>0.6002274990081787</v>
       </c>
       <c r="B39" t="n">
-        <v>0.009707722934345388</v>
+        <v>0.05306900127418033</v>
       </c>
       <c r="C39" t="n">
-        <v>0.01782498359680176</v>
+        <v>0.01794900894165039</v>
       </c>
       <c r="D39" t="n">
-        <v>0.000784860384303361</v>
+        <v>0.001453627480275412</v>
       </c>
       <c r="E39" t="n">
         <v>20</v>
@@ -2727,42 +2727,42 @@
         </is>
       </c>
       <c r="K39" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="L39" t="n">
-        <v>0.815028901734104</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M39" t="n">
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="N39" t="n">
         <v>0.7572254335260116</v>
       </c>
-      <c r="N39" t="n">
-        <v>0.815028901734104</v>
-      </c>
       <c r="O39" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P39" t="n">
-        <v>0.8206412152170991</v>
+        <v>0.8136779136980777</v>
       </c>
       <c r="Q39" t="n">
-        <v>0.0371269939385604</v>
+        <v>0.02852279584984272</v>
       </c>
       <c r="R39" t="n">
-        <v>4</v>
+        <v>42</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>0.8407991409301758</v>
+        <v>0.8571742057800293</v>
       </c>
       <c r="B40" t="n">
-        <v>0.05785147201423303</v>
+        <v>0.03397275847065408</v>
       </c>
       <c r="C40" t="n">
-        <v>0.02941017150878906</v>
+        <v>0.03098359107971192</v>
       </c>
       <c r="D40" t="n">
-        <v>0.002480455121743329</v>
+        <v>0.003549833321697725</v>
       </c>
       <c r="E40" t="n">
         <v>20</v>
@@ -2785,42 +2785,42 @@
         </is>
       </c>
       <c r="K40" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L40" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M40" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8554913294797688</v>
       </c>
       <c r="N40" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O40" t="n">
-        <v>0.8255813953488372</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P40" t="n">
-        <v>0.8136711923645651</v>
+        <v>0.8241027019760722</v>
       </c>
       <c r="Q40" t="n">
-        <v>0.02132578184640781</v>
+        <v>0.03057448842415795</v>
       </c>
       <c r="R40" t="n">
-        <v>23</v>
+        <v>17</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>1.182647800445557</v>
+        <v>1.206933116912842</v>
       </c>
       <c r="B41" t="n">
-        <v>0.06816528463327061</v>
+        <v>0.02270391393021826</v>
       </c>
       <c r="C41" t="n">
-        <v>0.03034734725952148</v>
+        <v>0.03321657180786133</v>
       </c>
       <c r="D41" t="n">
-        <v>0.001927882127538542</v>
+        <v>0.003938015002160865</v>
       </c>
       <c r="E41" t="n">
         <v>20</v>
@@ -2843,42 +2843,42 @@
         </is>
       </c>
       <c r="K41" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8554913294797688</v>
       </c>
       <c r="L41" t="n">
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="M41" t="n">
+        <v>0.838150289017341</v>
+      </c>
+      <c r="N41" t="n">
         <v>0.7687861271676301</v>
-      </c>
-      <c r="M41" t="n">
-        <v>0.791907514450867</v>
-      </c>
-      <c r="N41" t="n">
-        <v>0.8092485549132948</v>
       </c>
       <c r="O41" t="n">
         <v>0.8430232558139535</v>
       </c>
       <c r="P41" t="n">
-        <v>0.8113792176367791</v>
+        <v>0.8252520500067213</v>
       </c>
       <c r="Q41" t="n">
-        <v>0.02918492173501122</v>
+        <v>0.03034710291041813</v>
       </c>
       <c r="R41" t="n">
-        <v>31</v>
+        <v>15</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>0.4041184902191162</v>
+        <v>0.4103041172027588</v>
       </c>
       <c r="B42" t="n">
-        <v>0.01330393512958267</v>
+        <v>0.017724450556209</v>
       </c>
       <c r="C42" t="n">
-        <v>0.01646733283996582</v>
+        <v>0.01737966537475586</v>
       </c>
       <c r="D42" t="n">
-        <v>0.001216032089750563</v>
+        <v>0.00183339070900503</v>
       </c>
       <c r="E42" t="n">
         <v>20</v>
@@ -2901,42 +2901,42 @@
         </is>
       </c>
       <c r="K42" t="n">
-        <v>0.861271676300578</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L42" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8497109826589595</v>
       </c>
       <c r="M42" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="N42" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="O42" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P42" t="n">
-        <v>0.8148474257292648</v>
+        <v>0.824102701976072</v>
       </c>
       <c r="Q42" t="n">
-        <v>0.03128336792934412</v>
+        <v>0.02531343793231531</v>
       </c>
       <c r="R42" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>0.5497878551483154</v>
+        <v>0.583936071395874</v>
       </c>
       <c r="B43" t="n">
-        <v>0.008878008377001197</v>
+        <v>0.02909011227836133</v>
       </c>
       <c r="C43" t="n">
-        <v>0.01679444313049316</v>
+        <v>0.01993007659912109</v>
       </c>
       <c r="D43" t="n">
-        <v>0.0008558283490854416</v>
+        <v>0.002062619807213166</v>
       </c>
       <c r="E43" t="n">
         <v>20</v>
@@ -2962,39 +2962,39 @@
         <v>0.838150289017341</v>
       </c>
       <c r="L43" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M43" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="N43" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="O43" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8255813953488372</v>
       </c>
       <c r="P43" t="n">
-        <v>0.803306896088184</v>
+        <v>0.82291974727786</v>
       </c>
       <c r="Q43" t="n">
-        <v>0.04162049435739143</v>
+        <v>0.02178432200419637</v>
       </c>
       <c r="R43" t="n">
-        <v>42</v>
+        <v>24</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>0.8919825077056884</v>
+        <v>0.8532904148101806</v>
       </c>
       <c r="B44" t="n">
-        <v>0.06527956844064675</v>
+        <v>0.03453210406557941</v>
       </c>
       <c r="C44" t="n">
-        <v>0.03222265243530274</v>
+        <v>0.02903871536254883</v>
       </c>
       <c r="D44" t="n">
-        <v>0.003759572123241582</v>
+        <v>0.001934516194206407</v>
       </c>
       <c r="E44" t="n">
         <v>20</v>
@@ -3017,42 +3017,42 @@
         </is>
       </c>
       <c r="K44" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L44" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="M44" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="N44" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O44" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="P44" t="n">
-        <v>0.8171730071246136</v>
+        <v>0.8218107272482861</v>
       </c>
       <c r="Q44" t="n">
-        <v>0.03221456270947134</v>
+        <v>0.03044748056780253</v>
       </c>
       <c r="R44" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>1.181973266601563</v>
+        <v>1.187806129455566</v>
       </c>
       <c r="B45" t="n">
-        <v>0.05590652346121351</v>
+        <v>0.0313367631627674</v>
       </c>
       <c r="C45" t="n">
-        <v>0.03289527893066406</v>
+        <v>0.03039002418518066</v>
       </c>
       <c r="D45" t="n">
-        <v>0.002673561939223759</v>
+        <v>0.001888073593759534</v>
       </c>
       <c r="E45" t="n">
         <v>20</v>
@@ -3078,39 +3078,39 @@
         <v>0.838150289017341</v>
       </c>
       <c r="L45" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M45" t="n">
-        <v>0.791907514450867</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="N45" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O45" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P45" t="n">
-        <v>0.8113926603038042</v>
+        <v>0.818302191154725</v>
       </c>
       <c r="Q45" t="n">
-        <v>0.03112893589387105</v>
+        <v>0.03084923385364757</v>
       </c>
       <c r="R45" t="n">
-        <v>30</v>
+        <v>34</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>0.4272167682647705</v>
+        <v>0.4022369384765625</v>
       </c>
       <c r="B46" t="n">
-        <v>0.03517374428557537</v>
+        <v>0.006478581908207064</v>
       </c>
       <c r="C46" t="n">
-        <v>0.01750173568725586</v>
+        <v>0.01687521934509277</v>
       </c>
       <c r="D46" t="n">
-        <v>0.002185973777720043</v>
+        <v>0.00113308207753991</v>
       </c>
       <c r="E46" t="n">
         <v>20</v>
@@ -3133,42 +3133,42 @@
         </is>
       </c>
       <c r="K46" t="n">
-        <v>0.8554913294797688</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L46" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M46" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8439306358381503</v>
       </c>
       <c r="N46" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="O46" t="n">
         <v>0.8546511627906976</v>
       </c>
       <c r="P46" t="n">
-        <v>0.8125487296679662</v>
+        <v>0.8264215620379083</v>
       </c>
       <c r="Q46" t="n">
-        <v>0.03516672349286269</v>
+        <v>0.02566414266027633</v>
       </c>
       <c r="R46" t="n">
-        <v>26</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>0.5948580741882324</v>
+        <v>0.6090811729431153</v>
       </c>
       <c r="B47" t="n">
-        <v>0.02347648806329375</v>
+        <v>0.0374588046026105</v>
       </c>
       <c r="C47" t="n">
-        <v>0.01845965385437012</v>
+        <v>0.01910576820373535</v>
       </c>
       <c r="D47" t="n">
-        <v>0.001914622032228247</v>
+        <v>0.004060654346336648</v>
       </c>
       <c r="E47" t="n">
         <v>20</v>
@@ -3191,42 +3191,42 @@
         </is>
       </c>
       <c r="K47" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="L47" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8323699421965318</v>
       </c>
       <c r="M47" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N47" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O47" t="n">
         <v>0.8546511627906976</v>
       </c>
       <c r="P47" t="n">
-        <v>0.8079244522113187</v>
+        <v>0.8229533539454227</v>
       </c>
       <c r="Q47" t="n">
-        <v>0.0327428132259811</v>
+        <v>0.02631029408932139</v>
       </c>
       <c r="R47" t="n">
-        <v>37</v>
+        <v>20</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>0.7537871837615967</v>
+        <v>0.7423183917999268</v>
       </c>
       <c r="B48" t="n">
-        <v>0.02464808865675771</v>
+        <v>0.03034326185976563</v>
       </c>
       <c r="C48" t="n">
-        <v>0.02428708076477051</v>
+        <v>0.02483620643615723</v>
       </c>
       <c r="D48" t="n">
-        <v>0.003093351953491286</v>
+        <v>0.003442524143413804</v>
       </c>
       <c r="E48" t="n">
         <v>20</v>
@@ -3249,42 +3249,42 @@
         </is>
       </c>
       <c r="K48" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L48" t="n">
-        <v>0.7630057803468208</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M48" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.861271676300578</v>
       </c>
       <c r="N48" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7861271676300579</v>
       </c>
       <c r="O48" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8662790697674418</v>
       </c>
       <c r="P48" t="n">
-        <v>0.8148608683962898</v>
+        <v>0.829903212797419</v>
       </c>
       <c r="Q48" t="n">
-        <v>0.03409738519319742</v>
+        <v>0.03053234532778314</v>
       </c>
       <c r="R48" t="n">
-        <v>17</v>
+        <v>4</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>0.8733252048492431</v>
+        <v>0.9081438064575196</v>
       </c>
       <c r="B49" t="n">
-        <v>0.05555225834830128</v>
+        <v>0.009158715293297022</v>
       </c>
       <c r="C49" t="n">
-        <v>0.0171567440032959</v>
+        <v>0.01693148612976074</v>
       </c>
       <c r="D49" t="n">
-        <v>0.0008169536601464008</v>
+        <v>0.0006701509593117412</v>
       </c>
       <c r="E49" t="n">
         <v>20</v>
@@ -3307,28 +3307,28 @@
         </is>
       </c>
       <c r="K49" t="n">
-        <v>0.8554913294797688</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="L49" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="M49" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="N49" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O49" t="n">
         <v>0.8372093023255814</v>
       </c>
       <c r="P49" t="n">
-        <v>0.8090603575749429</v>
+        <v>0.8206210512165614</v>
       </c>
       <c r="Q49" t="n">
-        <v>0.03767378843539248</v>
+        <v>0.02913712884750969</v>
       </c>
       <c r="R49" t="n">
-        <v>36</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -3439,16 +3439,16 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1.937149333953857</v>
+        <v>1.861059188842773</v>
       </c>
       <c r="B2" t="n">
-        <v>0.08207628206444069</v>
+        <v>0.06050492962374082</v>
       </c>
       <c r="C2" t="n">
-        <v>0.007100963592529297</v>
+        <v>0.007248783111572265</v>
       </c>
       <c r="D2" t="n">
-        <v>0.0002216853128959615</v>
+        <v>0.0003233128447416897</v>
       </c>
       <c r="E2" t="n">
         <v>0.01</v>
@@ -3471,42 +3471,42 @@
         </is>
       </c>
       <c r="K2" t="n">
-        <v>0.7398843930635838</v>
+        <v>0.7225433526011561</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6358381502890174</v>
+        <v>0.7283236994219653</v>
       </c>
       <c r="M2" t="n">
-        <v>0.6820809248554913</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="N2" t="n">
-        <v>0.7225433526011561</v>
+        <v>0.6994219653179191</v>
       </c>
       <c r="O2" t="n">
-        <v>0.7616279069767442</v>
+        <v>0.7441860465116279</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7083949455571986</v>
+        <v>0.7280279607474123</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.04468204814623513</v>
+        <v>0.01685592522695908</v>
       </c>
       <c r="R2" t="n">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>6.137348461151123</v>
+        <v>6.120107460021972</v>
       </c>
       <c r="B3" t="n">
-        <v>0.2022243998199624</v>
+        <v>0.1384632665638055</v>
       </c>
       <c r="C3" t="n">
-        <v>0.007037305831909179</v>
+        <v>0.008925819396972656</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0003387764954317626</v>
+        <v>0.003427157488522186</v>
       </c>
       <c r="E3" t="n">
         <v>0.01</v>
@@ -3529,42 +3529,42 @@
         </is>
       </c>
       <c r="K3" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="L3" t="n">
-        <v>0.6473988439306358</v>
+        <v>0.7167630057803468</v>
       </c>
       <c r="M3" t="n">
-        <v>0.6763005780346821</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="N3" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.6936416184971098</v>
       </c>
       <c r="O3" t="n">
-        <v>0.7848837209302325</v>
+        <v>0.7209302325581395</v>
       </c>
       <c r="P3" t="n">
-        <v>0.7280750100820004</v>
+        <v>0.7268450060492001</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.05673784771640297</v>
+        <v>0.02213334207194946</v>
       </c>
       <c r="R3" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2.189432525634766</v>
+        <v>2.031331014633179</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1108323157039978</v>
+        <v>0.06293959354029013</v>
       </c>
       <c r="C4" t="n">
-        <v>0.006625032424926758</v>
+        <v>0.006459808349609375</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0004345143537811571</v>
+        <v>0.0002071859702140895</v>
       </c>
       <c r="E4" t="n">
         <v>0.01</v>
@@ -3587,42 +3587,42 @@
         </is>
       </c>
       <c r="K4" t="n">
-        <v>0.7225433526011561</v>
+        <v>0.7167630057803468</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6473988439306358</v>
+        <v>0.7283236994219653</v>
       </c>
       <c r="M4" t="n">
+        <v>0.7283236994219653</v>
+      </c>
+      <c r="N4" t="n">
         <v>0.6936416184971098</v>
       </c>
-      <c r="N4" t="n">
-        <v>0.7167630057803468</v>
-      </c>
       <c r="O4" t="n">
-        <v>0.7325581395348837</v>
+        <v>0.7383720930232558</v>
       </c>
       <c r="P4" t="n">
-        <v>0.7025809920688264</v>
+        <v>0.7210848232289286</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03040801405596269</v>
+        <v>0.01533270978026696</v>
       </c>
       <c r="R4" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>7.530782270431518</v>
+        <v>7.410306262969971</v>
       </c>
       <c r="B5" t="n">
-        <v>0.113303081980673</v>
+        <v>0.2675164705211875</v>
       </c>
       <c r="C5" t="n">
-        <v>0.006968355178833008</v>
+        <v>0.006661462783813477</v>
       </c>
       <c r="D5" t="n">
-        <v>0.000639576004655558</v>
+        <v>0.0005316854142006192</v>
       </c>
       <c r="E5" t="n">
         <v>0.01</v>
@@ -3645,42 +3645,42 @@
         </is>
       </c>
       <c r="K5" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6416184971098265</v>
+        <v>0.7225433526011561</v>
       </c>
       <c r="M5" t="n">
-        <v>0.6763005780346821</v>
+        <v>0.7341040462427746</v>
       </c>
       <c r="N5" t="n">
-        <v>0.7341040462427746</v>
+        <v>0.6647398843930635</v>
       </c>
       <c r="O5" t="n">
-        <v>0.7848837209302325</v>
+        <v>0.7151162790697675</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7165143164403818</v>
+        <v>0.7175897298023928</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.05110782672260753</v>
+        <v>0.02912960808407428</v>
       </c>
       <c r="R5" t="n">
-        <v>30</v>
+        <v>32</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>3.683712482452393</v>
+        <v>3.802878093719483</v>
       </c>
       <c r="B6" t="n">
-        <v>0.09110847988578098</v>
+        <v>0.1130669854611824</v>
       </c>
       <c r="C6" t="n">
-        <v>0.009426450729370118</v>
+        <v>0.009602165222167969</v>
       </c>
       <c r="D6" t="n">
-        <v>0.0003170376772892432</v>
+        <v>0.0001678329700593041</v>
       </c>
       <c r="E6" t="n">
         <v>0.01</v>
@@ -3703,42 +3703,42 @@
         </is>
       </c>
       <c r="K6" t="n">
+        <v>0.7398843930635838</v>
+      </c>
+      <c r="L6" t="n">
         <v>0.7745664739884393</v>
       </c>
-      <c r="L6" t="n">
-        <v>0.6936416184971098</v>
-      </c>
       <c r="M6" t="n">
-        <v>0.7283236994219653</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="N6" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.7167630057803468</v>
       </c>
       <c r="O6" t="n">
-        <v>0.7790697674418605</v>
+        <v>0.7848837209302325</v>
       </c>
       <c r="P6" t="n">
-        <v>0.748877537303401</v>
+        <v>0.7558206748218846</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.03298881979445529</v>
+        <v>0.02460551956017787</v>
       </c>
       <c r="R6" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>12.21805367469788</v>
+        <v>12.51967673301697</v>
       </c>
       <c r="B7" t="n">
-        <v>0.2881385946992981</v>
+        <v>0.2379723977734637</v>
       </c>
       <c r="C7" t="n">
-        <v>0.009452438354492188</v>
+        <v>0.009792709350585937</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0005173231491905309</v>
+        <v>0.001722018189096011</v>
       </c>
       <c r="E7" t="n">
         <v>0.01</v>
@@ -3761,42 +3761,42 @@
         </is>
       </c>
       <c r="K7" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="L7" t="n">
-        <v>0.6763005780346821</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="M7" t="n">
+        <v>0.7976878612716763</v>
+      </c>
+      <c r="N7" t="n">
         <v>0.7283236994219653</v>
       </c>
-      <c r="N7" t="n">
-        <v>0.7803468208092486</v>
-      </c>
       <c r="O7" t="n">
-        <v>0.8081395348837209</v>
+        <v>0.7558139534883721</v>
       </c>
       <c r="P7" t="n">
-        <v>0.7604718376125824</v>
+        <v>0.7604113456109692</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.05131217438169536</v>
+        <v>0.02390866667934582</v>
       </c>
       <c r="R7" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>4.110071277618408</v>
+        <v>4.438843679428101</v>
       </c>
       <c r="B8" t="n">
-        <v>0.1043749376964382</v>
+        <v>0.1152828481408348</v>
       </c>
       <c r="C8" t="n">
-        <v>0.008542299270629883</v>
+        <v>0.009121942520141601</v>
       </c>
       <c r="D8" t="n">
-        <v>0.000391841061687536</v>
+        <v>0.0004153087242630257</v>
       </c>
       <c r="E8" t="n">
         <v>0.01</v>
@@ -3819,42 +3819,42 @@
         </is>
       </c>
       <c r="K8" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="L8" t="n">
+        <v>0.7803468208092486</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0.7514450867052023</v>
+      </c>
+      <c r="N8" t="n">
         <v>0.7052023121387283</v>
       </c>
-      <c r="M8" t="n">
-        <v>0.7225433526011561</v>
-      </c>
-      <c r="N8" t="n">
-        <v>0.7572254335260116</v>
-      </c>
       <c r="O8" t="n">
-        <v>0.7674418604651163</v>
+        <v>0.7732558139534884</v>
       </c>
       <c r="P8" t="n">
-        <v>0.7453958865438903</v>
+        <v>0.7523390240623739</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.02688735037472001</v>
+        <v>0.02625039670912849</v>
       </c>
       <c r="R8" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>15.0549033164978</v>
+        <v>15.24073328971863</v>
       </c>
       <c r="B9" t="n">
-        <v>0.3831494140727327</v>
+        <v>0.2959909928654121</v>
       </c>
       <c r="C9" t="n">
-        <v>0.008516645431518555</v>
+        <v>0.009631872177124023</v>
       </c>
       <c r="D9" t="n">
-        <v>0.000272070412744254</v>
+        <v>0.001376739970839042</v>
       </c>
       <c r="E9" t="n">
         <v>0.01</v>
@@ -3877,42 +3877,42 @@
         </is>
       </c>
       <c r="K9" t="n">
-        <v>0.791907514450867</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6878612716763006</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="M9" t="n">
-        <v>0.7167630057803468</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="N9" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.6994219653179191</v>
       </c>
       <c r="O9" t="n">
-        <v>0.8081395348837209</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="P9" t="n">
-        <v>0.7546914907917731</v>
+        <v>0.7523323027288613</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.04548677339865012</v>
+        <v>0.02754514985422906</v>
       </c>
       <c r="R9" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>3.283046627044678</v>
+        <v>3.17051568031311</v>
       </c>
       <c r="B10" t="n">
-        <v>0.1612208336067132</v>
+        <v>0.06996458763193032</v>
       </c>
       <c r="C10" t="n">
-        <v>0.008161306381225586</v>
+        <v>0.008301496505737305</v>
       </c>
       <c r="D10" t="n">
-        <v>0.000269387336792023</v>
+        <v>0.0005321348010313966</v>
       </c>
       <c r="E10" t="n">
         <v>0.01</v>
@@ -3935,42 +3935,42 @@
         </is>
       </c>
       <c r="K10" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="L10" t="n">
+        <v>0.8208092485549133</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.7861271676300579</v>
+      </c>
+      <c r="N10" t="n">
         <v>0.7225433526011561</v>
       </c>
-      <c r="M10" t="n">
-        <v>0.7630057803468208</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0.791907514450867</v>
-      </c>
       <c r="O10" t="n">
-        <v>0.8313953488372093</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="P10" t="n">
-        <v>0.7836201102298695</v>
+        <v>0.7801182954698213</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.03785047579242726</v>
+        <v>0.0335509041325226</v>
       </c>
       <c r="R10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>10.30706777572632</v>
+        <v>10.58534803390503</v>
       </c>
       <c r="B11" t="n">
-        <v>0.07631376090486819</v>
+        <v>0.2590725101079843</v>
       </c>
       <c r="C11" t="n">
-        <v>0.008227539062500001</v>
+        <v>0.009590721130371094</v>
       </c>
       <c r="D11" t="n">
-        <v>0.0001504239783249026</v>
+        <v>0.0004016426471970752</v>
       </c>
       <c r="E11" t="n">
         <v>0.01</v>
@@ -3993,42 +3993,42 @@
         </is>
       </c>
       <c r="K11" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="L11" t="n">
+        <v>0.7803468208092486</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0.7976878612716763</v>
+      </c>
+      <c r="N11" t="n">
         <v>0.7514450867052023</v>
       </c>
-      <c r="M11" t="n">
-        <v>0.7687861271676301</v>
-      </c>
-      <c r="N11" t="n">
-        <v>0.7803468208092486</v>
-      </c>
       <c r="O11" t="n">
-        <v>0.8313953488372093</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="P11" t="n">
-        <v>0.7905565264148408</v>
+        <v>0.7731415512837747</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.03062982109587548</v>
+        <v>0.01534033906291464</v>
       </c>
       <c r="R11" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>3.720137023925781</v>
+        <v>3.73913049697876</v>
       </c>
       <c r="B12" t="n">
-        <v>0.168886693458716</v>
+        <v>0.05375603369381973</v>
       </c>
       <c r="C12" t="n">
-        <v>0.008212709426879882</v>
+        <v>0.01010570526123047</v>
       </c>
       <c r="D12" t="n">
-        <v>0.0005278978143782935</v>
+        <v>0.003936661081319842</v>
       </c>
       <c r="E12" t="n">
         <v>0.01</v>
@@ -4051,42 +4051,42 @@
         </is>
       </c>
       <c r="K12" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6705202312138728</v>
+        <v>0.7861271676300579</v>
       </c>
       <c r="M12" t="n">
-        <v>0.7283236994219653</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="N12" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7052023121387283</v>
       </c>
       <c r="O12" t="n">
-        <v>0.8197674418604651</v>
+        <v>0.7790697674418605</v>
       </c>
       <c r="P12" t="n">
-        <v>0.7604852802796074</v>
+        <v>0.7569700228525339</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.05456091072175991</v>
+        <v>0.02834982943251503</v>
       </c>
       <c r="R12" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>12.43324584960937</v>
+        <v>12.9864860534668</v>
       </c>
       <c r="B13" t="n">
-        <v>0.3143324687989972</v>
+        <v>0.3461959829813512</v>
       </c>
       <c r="C13" t="n">
-        <v>0.007898187637329102</v>
+        <v>0.00846552848815918</v>
       </c>
       <c r="D13" t="n">
-        <v>0.0003158988988106848</v>
+        <v>0.0004774898115691828</v>
       </c>
       <c r="E13" t="n">
         <v>0.01</v>
@@ -4109,42 +4109,42 @@
         </is>
       </c>
       <c r="K13" t="n">
+        <v>0.7572254335260116</v>
+      </c>
+      <c r="L13" t="n">
         <v>0.7687861271676301</v>
       </c>
-      <c r="L13" t="n">
-        <v>0.7283236994219653</v>
-      </c>
       <c r="M13" t="n">
-        <v>0.7225433526011561</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="N13" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.7167630057803468</v>
       </c>
       <c r="O13" t="n">
-        <v>0.813953488372093</v>
+        <v>0.7674418604651163</v>
       </c>
       <c r="P13" t="n">
-        <v>0.760478558946095</v>
+        <v>0.7534883720930232</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.03307752810618108</v>
+        <v>0.01900213111827683</v>
       </c>
       <c r="R13" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>6.571012687683106</v>
+        <v>6.955748891830444</v>
       </c>
       <c r="B14" t="n">
-        <v>0.2983433907624488</v>
+        <v>0.3315263392855078</v>
       </c>
       <c r="C14" t="n">
-        <v>0.012005615234375</v>
+        <v>0.01306538581848144</v>
       </c>
       <c r="D14" t="n">
-        <v>0.0002822009723723433</v>
+        <v>0.000752128347199249</v>
       </c>
       <c r="E14" t="n">
         <v>0.01</v>
@@ -4167,42 +4167,42 @@
         </is>
       </c>
       <c r="K14" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7861271676300579</v>
       </c>
       <c r="L14" t="n">
-        <v>0.7341040462427746</v>
+        <v>0.838150289017341</v>
       </c>
       <c r="M14" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7861271676300579</v>
       </c>
       <c r="N14" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7630057803468208</v>
       </c>
       <c r="O14" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="P14" t="n">
-        <v>0.7928888291437021</v>
+        <v>0.7951471972039252</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.03797960499568215</v>
+        <v>0.02488609109411034</v>
       </c>
       <c r="R14" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>20.35375599861145</v>
+        <v>21.61655430793762</v>
       </c>
       <c r="B15" t="n">
-        <v>0.2838357183423897</v>
+        <v>0.401485451188493</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01140828132629395</v>
+        <v>0.01280035972595215</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0003419233119153608</v>
+        <v>0.001886056547937102</v>
       </c>
       <c r="E15" t="n">
         <v>0.01</v>
@@ -4225,42 +4225,42 @@
         </is>
       </c>
       <c r="K15" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7225433526011561</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="M15" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="N15" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O15" t="n">
-        <v>0.8488372093023255</v>
+        <v>0.7965116279069767</v>
       </c>
       <c r="P15" t="n">
-        <v>0.7952009678720259</v>
+        <v>0.7928283371420891</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.04465305158792152</v>
+        <v>0.02170634443839938</v>
       </c>
       <c r="R15" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>7.265549755096435</v>
+        <v>7.641671848297119</v>
       </c>
       <c r="B16" t="n">
-        <v>0.1053843010977708</v>
+        <v>0.4440121483115594</v>
       </c>
       <c r="C16" t="n">
-        <v>0.0117943286895752</v>
+        <v>0.01419696807861328</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0005111303999573053</v>
+        <v>0.003824151553123609</v>
       </c>
       <c r="E16" t="n">
         <v>0.01</v>
@@ -4283,42 +4283,42 @@
         </is>
       </c>
       <c r="K16" t="n">
+        <v>0.7745664739884393</v>
+      </c>
+      <c r="L16" t="n">
         <v>0.8208092485549133</v>
       </c>
-      <c r="L16" t="n">
-        <v>0.6936416184971098</v>
-      </c>
       <c r="M16" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="N16" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7398843930635838</v>
       </c>
       <c r="O16" t="n">
-        <v>0.8023255813953488</v>
+        <v>0.813953488372093</v>
       </c>
       <c r="P16" t="n">
-        <v>0.7720258099206883</v>
+        <v>0.7847560155934937</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.04349467098339674</v>
+        <v>0.02957513837105901</v>
       </c>
       <c r="R16" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>24.17790641784668</v>
+        <v>26.15577898025513</v>
       </c>
       <c r="B17" t="n">
-        <v>0.2441981346933244</v>
+        <v>0.6706459403213026</v>
       </c>
       <c r="C17" t="n">
-        <v>0.01090526580810547</v>
+        <v>0.01225070953369141</v>
       </c>
       <c r="D17" t="n">
-        <v>9.159990923142964e-05</v>
+        <v>0.001149899084076822</v>
       </c>
       <c r="E17" t="n">
         <v>0.01</v>
@@ -4341,42 +4341,42 @@
         </is>
       </c>
       <c r="K17" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="L17" t="n">
-        <v>0.7225433526011561</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="N17" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O17" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="P17" t="n">
-        <v>0.7824909261997581</v>
+        <v>0.7858986422906304</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.0451869428456373</v>
+        <v>0.02049297442853987</v>
       </c>
       <c r="R17" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1.864797973632812</v>
+        <v>2.112496662139892</v>
       </c>
       <c r="B18" t="n">
-        <v>0.0621131847527002</v>
+        <v>0.1955990980400097</v>
       </c>
       <c r="C18" t="n">
-        <v>0.006434965133666992</v>
+        <v>0.006559848785400391</v>
       </c>
       <c r="D18" t="n">
-        <v>0.0001232473615102572</v>
+        <v>0.0004087557315035389</v>
       </c>
       <c r="E18" t="n">
         <v>0.1</v>
@@ -4399,42 +4399,42 @@
         </is>
       </c>
       <c r="K18" t="n">
-        <v>0.838150289017341</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="M18" t="n">
-        <v>0.7630057803468208</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O18" t="n">
-        <v>0.8255813953488372</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P18" t="n">
-        <v>0.7963301519021374</v>
+        <v>0.7986490119639736</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.03025837747699232</v>
+        <v>0.02818379130303592</v>
       </c>
       <c r="R18" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>6.070192813873291</v>
+        <v>6.65063591003418</v>
       </c>
       <c r="B19" t="n">
-        <v>0.1340912362873176</v>
+        <v>0.2253635928226442</v>
       </c>
       <c r="C19" t="n">
-        <v>0.006901931762695312</v>
+        <v>0.008895540237426757</v>
       </c>
       <c r="D19" t="n">
-        <v>0.0003835927892524986</v>
+        <v>0.001670045851599177</v>
       </c>
       <c r="E19" t="n">
         <v>0.1</v>
@@ -4457,42 +4457,42 @@
         </is>
       </c>
       <c r="K19" t="n">
-        <v>0.838150289017341</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="L19" t="n">
+        <v>0.8092485549132948</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0.8323699421965318</v>
+      </c>
+      <c r="N19" t="n">
         <v>0.7398843930635838</v>
       </c>
-      <c r="M19" t="n">
-        <v>0.7745664739884393</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0.7687861271676301</v>
-      </c>
       <c r="O19" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8313953488372093</v>
       </c>
       <c r="P19" t="n">
-        <v>0.7952076892055384</v>
+        <v>0.803273289420621</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.04373195452443947</v>
+        <v>0.03373828508075605</v>
       </c>
       <c r="R19" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2.027330636978149</v>
+        <v>2.321340847015381</v>
       </c>
       <c r="B20" t="n">
-        <v>0.06746944131392738</v>
+        <v>0.1290272700587892</v>
       </c>
       <c r="C20" t="n">
-        <v>0.00646061897277832</v>
+        <v>0.007848978042602539</v>
       </c>
       <c r="D20" t="n">
-        <v>0.0001700065507963302</v>
+        <v>0.0003208375352627833</v>
       </c>
       <c r="E20" t="n">
         <v>0.1</v>
@@ -4515,42 +4515,42 @@
         </is>
       </c>
       <c r="K20" t="n">
-        <v>0.8208092485549133</v>
+        <v>0.7861271676300579</v>
       </c>
       <c r="L20" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="M20" t="n">
         <v>0.7803468208092486</v>
       </c>
       <c r="N20" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8081395348837209</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7928417798091142</v>
+        <v>0.7905699690818658</v>
       </c>
       <c r="Q20" t="n">
-        <v>0.02449053611817975</v>
+        <v>0.03144119123966533</v>
       </c>
       <c r="R20" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>7.240244674682617</v>
+        <v>7.89335265159607</v>
       </c>
       <c r="B21" t="n">
-        <v>0.08887209627084544</v>
+        <v>0.2138459646065571</v>
       </c>
       <c r="C21" t="n">
-        <v>0.00685272216796875</v>
+        <v>0.007390546798706055</v>
       </c>
       <c r="D21" t="n">
-        <v>0.0004207732669218384</v>
+        <v>0.0004561015939671404</v>
       </c>
       <c r="E21" t="n">
         <v>0.1</v>
@@ -4573,42 +4573,42 @@
         </is>
       </c>
       <c r="K21" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="L21" t="n">
-        <v>0.7283236994219653</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N21" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7225433526011561</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.7848837209302325</v>
       </c>
       <c r="P21" t="n">
-        <v>0.7905901330824034</v>
+        <v>0.791658825110902</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.04927968057797401</v>
+        <v>0.03750258124867918</v>
       </c>
       <c r="R21" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>3.498468637466431</v>
+        <v>3.94059853553772</v>
       </c>
       <c r="B22" t="n">
-        <v>0.08707984910294518</v>
+        <v>0.07364344918964022</v>
       </c>
       <c r="C22" t="n">
-        <v>0.008530426025390624</v>
+        <v>0.01023173332214355</v>
       </c>
       <c r="D22" t="n">
-        <v>0.0003734431236679706</v>
+        <v>0.0009258619289318559</v>
       </c>
       <c r="E22" t="n">
         <v>0.1</v>
@@ -4631,42 +4631,42 @@
         </is>
       </c>
       <c r="K22" t="n">
-        <v>0.8265895953757225</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="L22" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="M22" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="N22" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O22" t="n">
-        <v>0.8372093023255814</v>
+        <v>0.8255813953488372</v>
       </c>
       <c r="P22" t="n">
-        <v>0.80096787202581</v>
+        <v>0.7951740825379756</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.03261032541477882</v>
+        <v>0.02443393236225376</v>
       </c>
       <c r="R22" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>12.0231737613678</v>
+        <v>12.97383847236633</v>
       </c>
       <c r="B23" t="n">
-        <v>0.08993545761952523</v>
+        <v>0.1301578614333106</v>
       </c>
       <c r="C23" t="n">
-        <v>0.008576393127441406</v>
+        <v>0.009744596481323243</v>
       </c>
       <c r="D23" t="n">
-        <v>0.0001849935216771577</v>
+        <v>0.001314615298520118</v>
       </c>
       <c r="E23" t="n">
         <v>0.1</v>
@@ -4689,42 +4689,42 @@
         </is>
       </c>
       <c r="K23" t="n">
+        <v>0.7803468208092486</v>
+      </c>
+      <c r="L23" t="n">
         <v>0.8265895953757225</v>
       </c>
-      <c r="L23" t="n">
-        <v>0.7341040462427746</v>
-      </c>
       <c r="M23" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="N23" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O23" t="n">
-        <v>0.8430232558139535</v>
+        <v>0.8081395348837209</v>
       </c>
       <c r="P23" t="n">
-        <v>0.7917260384460277</v>
+        <v>0.7951539185374379</v>
       </c>
       <c r="Q23" t="n">
-        <v>0.03930585956528299</v>
+        <v>0.02640151097195898</v>
       </c>
       <c r="R23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>4.100957536697388</v>
+        <v>4.573363065719604</v>
       </c>
       <c r="B24" t="n">
-        <v>0.1174458513113844</v>
+        <v>0.069667985861186</v>
       </c>
       <c r="C24" t="n">
-        <v>0.008513402938842774</v>
+        <v>0.009018802642822265</v>
       </c>
       <c r="D24" t="n">
-        <v>0.0003710795171574392</v>
+        <v>0.0003650522652792477</v>
       </c>
       <c r="E24" t="n">
         <v>0.1</v>
@@ -4747,42 +4747,42 @@
         </is>
       </c>
       <c r="K24" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L24" t="n">
-        <v>0.7398843930635838</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="M24" t="n">
         <v>0.7803468208092486</v>
       </c>
       <c r="N24" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="O24" t="n">
-        <v>0.8197674418604651</v>
+        <v>0.8488372093023255</v>
       </c>
       <c r="P24" t="n">
-        <v>0.7893870143836538</v>
+        <v>0.7975131066003496</v>
       </c>
       <c r="Q24" t="n">
-        <v>0.03323367416361914</v>
+        <v>0.03403022773366199</v>
       </c>
       <c r="R24" t="n">
-        <v>19</v>
+        <v>9</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>14.77825713157654</v>
+        <v>15.3404411315918</v>
       </c>
       <c r="B25" t="n">
-        <v>0.2494407052791754</v>
+        <v>0.2020072669687655</v>
       </c>
       <c r="C25" t="n">
-        <v>0.009353494644165039</v>
+        <v>0.00892033576965332</v>
       </c>
       <c r="D25" t="n">
-        <v>0.001513322273214059</v>
+        <v>0.0005407330346485078</v>
       </c>
       <c r="E25" t="n">
         <v>0.1</v>
@@ -4805,42 +4805,42 @@
         </is>
       </c>
       <c r="K25" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L25" t="n">
-        <v>0.7167630057803468</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="M25" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N25" t="n">
-        <v>0.7687861271676301</v>
+        <v>0.7283236994219653</v>
       </c>
       <c r="O25" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8081395348837209</v>
       </c>
       <c r="P25" t="n">
-        <v>0.7894273423847291</v>
+        <v>0.793997849173276</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.0490412573579269</v>
+        <v>0.03412185034745407</v>
       </c>
       <c r="R25" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>3.19264554977417</v>
+        <v>3.213704824447632</v>
       </c>
       <c r="B26" t="n">
-        <v>0.1299822309360759</v>
+        <v>0.2448370964629991</v>
       </c>
       <c r="C26" t="n">
-        <v>0.008490657806396485</v>
+        <v>0.0103510856628418</v>
       </c>
       <c r="D26" t="n">
-        <v>0.0005578126513745941</v>
+        <v>0.00304825212466271</v>
       </c>
       <c r="E26" t="n">
         <v>0.1</v>
@@ -4863,42 +4863,42 @@
         </is>
       </c>
       <c r="K26" t="n">
-        <v>0.8497109826589595</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L26" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="M26" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="N26" t="n">
-        <v>0.8034682080924855</v>
+        <v>0.7745664739884393</v>
       </c>
       <c r="O26" t="n">
-        <v>0.8313953488372093</v>
+        <v>0.8430232558139535</v>
       </c>
       <c r="P26" t="n">
-        <v>0.8044293587847828</v>
+        <v>0.8090670789084553</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.03441167586651481</v>
+        <v>0.0219555792874759</v>
       </c>
       <c r="R26" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>10.06833891868591</v>
+        <v>10.33016014099121</v>
       </c>
       <c r="B27" t="n">
-        <v>0.1672243847052706</v>
+        <v>0.2184797770570385</v>
       </c>
       <c r="C27" t="n">
-        <v>0.008648157119750977</v>
+        <v>0.00829453468322754</v>
       </c>
       <c r="D27" t="n">
-        <v>0.0005809977539791645</v>
+        <v>0.0003541617398754885</v>
       </c>
       <c r="E27" t="n">
         <v>0.1</v>
@@ -4921,42 +4921,42 @@
         </is>
       </c>
       <c r="K27" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="L27" t="n">
-        <v>0.7398843930635838</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="M27" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N27" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7572254335260116</v>
       </c>
       <c r="O27" t="n">
-        <v>0.8662790697674418</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="P27" t="n">
-        <v>0.8021575480575347</v>
+        <v>0.8102164269391047</v>
       </c>
       <c r="Q27" t="n">
-        <v>0.04355014385955983</v>
+        <v>0.02799244896479365</v>
       </c>
       <c r="R27" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>3.518688631057739</v>
+        <v>3.451508140563965</v>
       </c>
       <c r="B28" t="n">
-        <v>0.04484541508449662</v>
+        <v>0.09232324060409154</v>
       </c>
       <c r="C28" t="n">
-        <v>0.008151006698608399</v>
+        <v>0.008113527297973632</v>
       </c>
       <c r="D28" t="n">
-        <v>0.0006116338648451829</v>
+        <v>0.0007525798613770979</v>
       </c>
       <c r="E28" t="n">
         <v>0.1</v>
@@ -4979,42 +4979,42 @@
         </is>
       </c>
       <c r="K28" t="n">
-        <v>0.838150289017341</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="L28" t="n">
-        <v>0.7514450867052023</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="M28" t="n">
-        <v>0.7745664739884393</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="N28" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7283236994219653</v>
       </c>
       <c r="O28" t="n">
-        <v>0.8081395348837209</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="P28" t="n">
-        <v>0.793997849173276</v>
+        <v>0.792875386476677</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.02950036387382812</v>
+        <v>0.03712779945495191</v>
       </c>
       <c r="R28" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>12.47424964904785</v>
+        <v>11.94939227104187</v>
       </c>
       <c r="B29" t="n">
-        <v>0.1190288477133892</v>
+        <v>0.127936988910338</v>
       </c>
       <c r="C29" t="n">
-        <v>0.008534860610961915</v>
+        <v>0.008012866973876953</v>
       </c>
       <c r="D29" t="n">
-        <v>0.0001958621846953698</v>
+        <v>0.0003226238631595916</v>
       </c>
       <c r="E29" t="n">
         <v>0.1</v>
@@ -5037,42 +5037,42 @@
         </is>
       </c>
       <c r="K29" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.7803468208092486</v>
       </c>
       <c r="L29" t="n">
-        <v>0.7398843930635838</v>
+        <v>0.7976878612716763</v>
       </c>
       <c r="M29" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8497109826589595</v>
       </c>
       <c r="N29" t="n">
-        <v>0.7861271676300579</v>
+        <v>0.7456647398843931</v>
       </c>
       <c r="O29" t="n">
-        <v>0.8546511627906976</v>
+        <v>0.8197674418604651</v>
       </c>
       <c r="P29" t="n">
-        <v>0.8009880360263477</v>
+        <v>0.7986355692969485</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.03975301667520711</v>
+        <v>0.03520380413688997</v>
       </c>
       <c r="R29" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>6.554072856903076</v>
+        <v>6.134332752227783</v>
       </c>
       <c r="B30" t="n">
-        <v>0.2891003759778088</v>
+        <v>0.1300881815429141</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0111846923828125</v>
+        <v>0.01080183982849121</v>
       </c>
       <c r="D30" t="n">
-        <v>0.0003425401470107594</v>
+        <v>0.0003846977980127801</v>
       </c>
       <c r="E30" t="n">
         <v>0.1</v>
@@ -5095,25 +5095,25 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>0.8323699421965318</v>
+        <v>0.8034682080924855</v>
       </c>
       <c r="L30" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="M30" t="n">
-        <v>0.791907514450867</v>
+        <v>0.8265895953757225</v>
       </c>
       <c r="N30" t="n">
-        <v>0.8092485549132948</v>
+        <v>0.7687861271676301</v>
       </c>
       <c r="O30" t="n">
         <v>0.8430232558139535</v>
       </c>
       <c r="P30" t="n">
-        <v>0.8113792176367791</v>
+        <v>0.812535287000941</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.02361631754175367</v>
+        <v>0.02526538807177138</v>
       </c>
       <c r="R30" t="n">
         <v>1</v>
@@ -5121,16 +5121,16 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>19.19124202728272</v>
+        <v>18.51515936851501</v>
       </c>
       <c r="B31" t="n">
-        <v>0.7995169435844121</v>
+        <v>0.6130035541379737</v>
       </c>
       <c r="C31" t="n">
-        <v>0.008614540100097656</v>
+        <v>0.008660793304443359</v>
       </c>
       <c r="D31" t="n">
-        <v>0.0008069515805897283</v>
+        <v>0.001120866410942859</v>
       </c>
       <c r="E31" t="n">
         <v>0.1</v>
@@ -5153,42 +5153,42 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.7861271676300579</v>
       </c>
       <c r="L31" t="n">
-        <v>0.7456647398843931</v>
+        <v>0.8208092485549133</v>
       </c>
       <c r="M31" t="n">
-        <v>0.791907514450867</v>
+        <v>0.815028901734104</v>
       </c>
       <c r="N31" t="n">
-        <v>0.7803468208092486</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O31" t="n">
-        <v>0.8662790697674418</v>
+        <v>0.8372093023255814</v>
       </c>
       <c r="P31" t="n">
-        <v>0.8056257561500202</v>
+        <v>0.8021239413899718</v>
       </c>
       <c r="Q31" t="n">
-        <v>0.0437461460235791</v>
+        <v>0.0302354240592048</v>
       </c>
       <c r="R31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>7.187092256546021</v>
+        <v>6.655961036682129</v>
       </c>
       <c r="B32" t="n">
-        <v>0.1671879848161952</v>
+        <v>0.155212248743568</v>
       </c>
       <c r="C32" t="n">
-        <v>0.01135244369506836</v>
+        <v>0.01085567474365234</v>
       </c>
       <c r="D32" t="n">
-        <v>0.0004262775273463407</v>
+        <v>0.0003231742864798904</v>
       </c>
       <c r="E32" t="n">
         <v>0.1</v>
@@ -5211,42 +5211,42 @@
         </is>
       </c>
       <c r="K32" t="n">
-        <v>0.8439306358381503</v>
+        <v>0.8092485549132948</v>
       </c>
       <c r="L32" t="n">
+        <v>0.815028901734104</v>
+      </c>
+      <c r="M32" t="n">
+        <v>0.8092485549132948</v>
+      </c>
+      <c r="N32" t="n">
         <v>0.7398843930635838</v>
-      </c>
-      <c r="M32" t="n">
-        <v>0.7687861271676301</v>
-      </c>
-      <c r="N32" t="n">
-        <v>0.791907514450867</v>
       </c>
       <c r="O32" t="n">
         <v>0.8313953488372093</v>
       </c>
       <c r="P32" t="n">
-        <v>0.795180803871488</v>
+        <v>0.8009611506922972</v>
       </c>
       <c r="Q32" t="n">
-        <v>0.03860861513709318</v>
+        <v>0.03159707105406782</v>
       </c>
       <c r="R32" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>19.19946336746216</v>
+        <v>18.6383339881897</v>
       </c>
       <c r="B33" t="n">
-        <v>0.6878152467733617</v>
+        <v>1.073970236313387</v>
       </c>
       <c r="C33" t="n">
-        <v>0.007527780532836914</v>
+        <v>0.007403326034545898</v>
       </c>
       <c r="D33" t="n">
-        <v>0.0003965181643563824</v>
+        <v>0.0002432788600399217</v>
       </c>
       <c r="E33" t="n">
         <v>0.1</v>
@@ -5269,28 +5269,28 @@
         </is>
       </c>
       <c r="K33" t="n">
+        <v>0.791907514450867</v>
+      </c>
+      <c r="L33" t="n">
+        <v>0.7861271676300579</v>
+      </c>
+      <c r="M33" t="n">
         <v>0.838150289017341</v>
       </c>
-      <c r="L33" t="n">
-        <v>0.7283236994219653</v>
-      </c>
-      <c r="M33" t="n">
-        <v>0.7976878612716763</v>
-      </c>
       <c r="N33" t="n">
-        <v>0.7976878612716763</v>
+        <v>0.7514450867052023</v>
       </c>
       <c r="O33" t="n">
-        <v>0.8604651162790697</v>
+        <v>0.8023255813953488</v>
       </c>
       <c r="P33" t="n">
-        <v>0.8044629654523459</v>
+        <v>0.7939911278397633</v>
       </c>
       <c r="Q33" t="n">
-        <v>0.04507786279573318</v>
+        <v>0.02791359368886592</v>
       </c>
       <c r="R33" t="n">
-        <v>3</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>
